--- a/Techniques/Univariate Statistical Monitoring/items_mhi_ansaldo.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/items_mhi_ansaldo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data driven predictive maintenance\Univariate Statistical Monitoring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data driven predictive maintenance\Techniques\Univariate Statistical Monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6373EA-902F-4310-8D79-23A57D8D8141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3D4666-D414-4078-A793-1C5D9FEDFDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Techniques/Univariate Statistical Monitoring/items_mhi_ansaldo.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/items_mhi_ansaldo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data driven predictive maintenance\Techniques\Univariate Statistical Monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3D4666-D414-4078-A793-1C5D9FEDFDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CB73E3-0F89-4CC3-9B47-803CB5579C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Techniques/Univariate Statistical Monitoring/items_mhi_ansaldo.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/items_mhi_ansaldo.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data driven predictive maintenance\Techniques\Univariate Statistical Monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CB73E3-0F89-4CC3-9B47-803CB5579C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB61CD1-F2F4-4623-9B75-A00C04E39E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mitsubishi" sheetId="1" r:id="rId1"/>
     <sheet name="Ansaldo" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mitsubishi!$E$1:$E$166</definedName>
